--- a/data_analisys/sites_cumsum.xlsx
+++ b/data_analisys/sites_cumsum.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -627,7 +627,18 @@
         <v>2024</v>
       </c>
       <c r="C23">
-        <v>99</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>2025</v>
+      </c>
+      <c r="C24">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
